--- a/tame_output/ON/bt/strategyON_20230722.xlsx
+++ b/tame_output/ON/bt/strategyON_20230722.xlsx
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>105.4%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>142.4%</t>
+          <t>141.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>136.7%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1665"/>
+  <dimension ref="A1:G1666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39805,7 +39805,7 @@
         <v>45127</v>
       </c>
       <c r="B1665" t="n">
-        <v>2.900931382910476</v>
+        <v>2.901127389321589</v>
       </c>
       <c r="C1665" t="n">
         <v>3.018924541289277</v>
@@ -39821,6 +39821,29 @@
       </c>
       <c r="G1665" t="n">
         <v>4.284562166782789</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="2" t="n">
+        <v>45128</v>
+      </c>
+      <c r="B1666" t="n">
+        <v>2.902455588689966</v>
+      </c>
+      <c r="C1666" t="n">
+        <v>3.009159615729503</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>1.491929563894453</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>3.605575016973537</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>2.111182724624788</v>
+      </c>
+      <c r="G1666" t="n">
+        <v>4.275869250504377</v>
       </c>
     </row>
   </sheetData>
